--- a/outputs/399-14.xlsx
+++ b/outputs/399-14.xlsx
@@ -99,7 +99,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,12 +121,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="等线"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -182,15 +176,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -383,111 +377,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P23"/>
+  <dimension ref="L6:P23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-    </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,17 +398,6 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
         <v>5</v>
       </c>
@@ -525,23 +407,11 @@
       <c r="N7" s="2" t="n">
         <v>39.4999990463257</v>
       </c>
-      <c r="O7" s="1"/>
       <c r="P7" s="2" t="n">
         <v>71.79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
         <v>5</v>
       </c>
@@ -551,23 +421,11 @@
       <c r="N8" s="2" t="n">
         <v>32.4700005054474</v>
       </c>
-      <c r="O8" s="1"/>
       <c r="P8" s="2" t="n">
         <v>64.61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
         <v>5</v>
       </c>
@@ -577,23 +435,11 @@
       <c r="N9" s="2" t="n">
         <v>24.2800002098084</v>
       </c>
-      <c r="O9" s="1"/>
       <c r="P9" s="2" t="n">
         <v>11.96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
         <v>5</v>
       </c>
@@ -603,23 +449,11 @@
       <c r="N10" s="2" t="n">
         <v>33.1500008106232</v>
       </c>
-      <c r="O10" s="1"/>
       <c r="P10" s="2" t="n">
         <v>17.27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
         <v>5</v>
       </c>
@@ -629,23 +463,11 @@
       <c r="N11" s="2" t="n">
         <v>16.4699997901917</v>
       </c>
-      <c r="O11" s="1"/>
       <c r="P11" s="2" t="n">
         <v>11.62</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
         <v>5</v>
       </c>
@@ -656,24 +478,13 @@
         <v>40</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>12.6199996471405</v>
+        <v>12.62</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>44.34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
         <v>5</v>
       </c>
@@ -683,23 +494,11 @@
       <c r="N13" s="2" t="n">
         <v>38.2700006961823</v>
       </c>
-      <c r="O13" s="1"/>
       <c r="P13" s="2" t="n">
         <v>36.46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
         <v>5</v>
       </c>
@@ -709,23 +508,11 @@
       <c r="N14" s="2" t="n">
         <v>27.4100000858307</v>
       </c>
-      <c r="O14" s="1"/>
       <c r="P14" s="2" t="n">
         <v>50.37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
         <v>5</v>
       </c>
@@ -736,24 +523,13 @@
         <v>40</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>1.41999983787537</v>
+        <v>1.42</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>51.38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
         <v>5</v>
       </c>
@@ -764,24 +540,13 @@
         <v>40</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>1.03999978303909</v>
+        <v>1.04</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>17.25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
         <v>5</v>
       </c>
@@ -791,23 +556,11 @@
       <c r="N17" s="2" t="n">
         <v>30.8899998664856</v>
       </c>
-      <c r="O17" s="1"/>
       <c r="P17" s="2" t="n">
         <v>42.93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
       <c r="L18" s="1" t="s">
         <v>5</v>
       </c>
@@ -818,24 +571,13 @@
         <v>40</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>16.1399998664856</v>
+        <v>16.14</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>70.65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -845,23 +587,11 @@
       <c r="N19" s="2" t="n">
         <v>14.5099997520447</v>
       </c>
-      <c r="O19" s="1"/>
       <c r="P19" s="2" t="n">
         <v>22.8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,23 +601,11 @@
       <c r="N20" s="2" t="n">
         <v>11.9800000190735</v>
       </c>
-      <c r="O20" s="1"/>
       <c r="P20" s="2" t="n">
         <v>9.89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
         <v>5</v>
       </c>
@@ -898,24 +616,13 @@
         <v>40</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>2.0600004196167</v>
+        <v>2.06</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>84.92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
         <v>5</v>
       </c>
@@ -926,24 +633,13 @@
         <v>40</v>
       </c>
       <c r="O22" s="2" t="n">
-        <v>16.8500002622604</v>
+        <v>16.85</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>21.36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
         <v>5</v>
       </c>
@@ -953,7 +649,6 @@
       <c r="N23" s="2" t="n">
         <v>36.1900001764298</v>
       </c>
-      <c r="O23" s="1"/>
       <c r="P23" s="2" t="n">
         <v>15.49</v>
       </c>

--- a/outputs/399-14.xlsx
+++ b/outputs/399-14.xlsx
@@ -99,7 +99,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,6 +121,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -176,15 +182,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -377,10 +383,111 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="L6:P23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
       <c r="L6" s="1" t="s">
         <v>0</v>
       </c>
@@ -398,6 +505,17 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
       <c r="L7" s="1" t="s">
         <v>5</v>
       </c>
@@ -407,11 +525,23 @@
       <c r="N7" s="2" t="n">
         <v>39.4999990463257</v>
       </c>
+      <c r="O7" s="1"/>
       <c r="P7" s="2" t="n">
         <v>71.79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
       <c r="L8" s="1" t="s">
         <v>5</v>
       </c>
@@ -421,11 +551,23 @@
       <c r="N8" s="2" t="n">
         <v>32.4700005054474</v>
       </c>
+      <c r="O8" s="1"/>
       <c r="P8" s="2" t="n">
         <v>64.61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
       <c r="L9" s="1" t="s">
         <v>5</v>
       </c>
@@ -435,11 +577,23 @@
       <c r="N9" s="2" t="n">
         <v>24.2800002098084</v>
       </c>
+      <c r="O9" s="1"/>
       <c r="P9" s="2" t="n">
         <v>11.96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
       <c r="L10" s="1" t="s">
         <v>5</v>
       </c>
@@ -449,11 +603,23 @@
       <c r="N10" s="2" t="n">
         <v>33.1500008106232</v>
       </c>
+      <c r="O10" s="1"/>
       <c r="P10" s="2" t="n">
         <v>17.27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
         <v>5</v>
       </c>
@@ -463,11 +629,23 @@
       <c r="N11" s="2" t="n">
         <v>16.4699997901917</v>
       </c>
+      <c r="O11" s="1"/>
       <c r="P11" s="2" t="n">
         <v>11.62</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
         <v>5</v>
       </c>
@@ -477,14 +655,25 @@
       <c r="N12" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>12.62</v>
+      <c r="O12" s="1" t="n">
+        <v>12.6199996471405</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>44.34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
         <v>5</v>
       </c>
@@ -494,11 +683,23 @@
       <c r="N13" s="2" t="n">
         <v>38.2700006961823</v>
       </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="2" t="n">
         <v>36.46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
         <v>5</v>
       </c>
@@ -508,45 +709,79 @@
       <c r="N14" s="2" t="n">
         <v>27.4100000858307</v>
       </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="2" t="n">
         <v>50.37</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N15" s="1" t="n">
+      <c r="N15" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>1.42</v>
+      <c r="O15" s="1" t="n">
+        <v>1.41999983787537</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>51.38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N16" s="1" t="n">
+      <c r="N16" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>1.04</v>
+      <c r="O16" s="1" t="n">
+        <v>1.03999978303909</v>
       </c>
       <c r="P16" s="2" t="n">
         <v>17.25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
         <v>5</v>
       </c>
@@ -556,28 +791,51 @@
       <c r="N17" s="2" t="n">
         <v>30.8899998664856</v>
       </c>
+      <c r="O17" s="1"/>
       <c r="P17" s="2" t="n">
         <v>42.93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="N18" s="1" t="n">
+      <c r="N18" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>16.14</v>
+      <c r="O18" s="1" t="n">
+        <v>16.1399998664856</v>
       </c>
       <c r="P18" s="2" t="n">
         <v>70.65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
         <v>5</v>
       </c>
@@ -587,11 +845,23 @@
       <c r="N19" s="2" t="n">
         <v>14.5099997520447</v>
       </c>
+      <c r="O19" s="1"/>
       <c r="P19" s="2" t="n">
         <v>22.8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
         <v>5</v>
       </c>
@@ -601,45 +871,79 @@
       <c r="N20" s="2" t="n">
         <v>11.9800000190735</v>
       </c>
+      <c r="O20" s="1"/>
       <c r="P20" s="2" t="n">
         <v>9.89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="1" t="n">
+      <c r="N21" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O21" s="2" t="n">
-        <v>2.06</v>
+      <c r="O21" s="1" t="n">
+        <v>2.0600004196167</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>84.92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N22" s="1" t="n">
+      <c r="N22" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>16.85</v>
+      <c r="O22" s="1" t="n">
+        <v>16.8500002622604</v>
       </c>
       <c r="P22" s="2" t="n">
         <v>21.36</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
       <c r="L23" s="1" t="s">
         <v>5</v>
       </c>
@@ -649,6 +953,7 @@
       <c r="N23" s="2" t="n">
         <v>36.1900001764298</v>
       </c>
+      <c r="O23" s="1"/>
       <c r="P23" s="2" t="n">
         <v>15.49</v>
       </c>
